--- a/artfynd/A 6239-2026 artfynd.xlsx
+++ b/artfynd/A 6239-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113966166</v>
+        <v>128228666</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjännavallen-Östra Bölan, Hls</t>
+          <t>Mon, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602433</v>
+        <v>602335</v>
       </c>
       <c r="R2" t="n">
-        <v>6826219</v>
+        <v>6826209</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +760,315 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128322554</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mon, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>602246</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6826312</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113966166</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjännavallen-Östra Bölan, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602433</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6826219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Viktor Bolin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Viktor Bolin, Max Ljungkvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128228665</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mon, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602446</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6826266</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
